--- a/Genostar/TABLA_RESUMEN_CYPS.xlsx
+++ b/Genostar/TABLA_RESUMEN_CYPS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ctoma\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ctoma\Fobos\Proyecto_Diana\TFM_GenoStaR\Genostar\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -517,7 +517,7 @@
         <v>3.1666739999999999E-2</v>
       </c>
       <c r="G5">
-        <v>32.729999999999997</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
